--- a/-PCB-/REMOTE/bom/Remote_BOM.xlsx
+++ b/-PCB-/REMOTE/bom/Remote_BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MenMe\GitHub\Sumec-Remote\-PCB-\REMOTE\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFF918B-2636-43C0-8DDE-CE8C75D7BB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC8C3E5-07C7-4DD1-8DA7-A7D3A92D647F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{ADB08104-A899-476E-9563-6F3362DB1FE2}"/>
   </bookViews>
@@ -817,8 +817,8 @@
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
     <cellStyle name="Poznámka" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Propojená buňka" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Špatně" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Správně" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Špatně" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Text upozornění" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Vstup" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Výpočet" xfId="11" builtinId="22" customBuiltin="1"/>
